--- a/docs/etl/controlefinanceiro/saida/2026/DRE_Balancete_032026.xlsx
+++ b/docs/etl/controlefinanceiro/saida/2026/DRE_Balancete_032026.xlsx
@@ -864,7 +864,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 10/08/2026 15:57 | Regime de Caixa | Efetivados (Pago / Recebido)</t>
+          <t>Gerado em: 11/08/2026 07:54 | Regime de Caixa | Efetivados (Pago / Recebido)</t>
         </is>
       </c>
     </row>
